--- a/uploads/Internship.xlsx
+++ b/uploads/Internship.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/net/Documents/KSU/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8277F2E7-AD7F-6D4A-B156-581F8FCA7BEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B39B4E9-F696-4147-8E36-3EB2856F547B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1968" uniqueCount="567">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1969" uniqueCount="567">
   <si>
     <t>Company</t>
   </si>
@@ -2537,6 +2537,9 @@
       <c r="D7" s="2" t="s">
         <v>423</v>
       </c>
+      <c r="F7" s="4" t="s">
+        <v>474</v>
+      </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
@@ -2552,7 +2555,7 @@
         <v>423</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.2">
